--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554999095</v>
+        <v>46157.93111409595</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93111409595</v>
+        <v>46157.93135396274</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93135396274</v>
+        <v>46157.9338330277</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9338330277</v>
+        <v>46157.93694927672</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93694927672</v>
+        <v>46158.28204576569</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204576569</v>
+        <v>46158.29651694779</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29651694779</v>
+        <v>46158.29806696016</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806696016</v>
+        <v>46158.33369770715</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33369770715</v>
+        <v>46158.37221253192</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221253192</v>
+        <v>46158.37275149982</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
